--- a/PCVX.xlsx
+++ b/PCVX.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D075B415-9C8B-4B85-928E-F3997E72D234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E27C9C9-4657-4566-A24B-FFA3BA7B0F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6970" yWindow="2250" windowWidth="29470" windowHeight="18090" xr2:uid="{DC9E7F46-E6E4-44BA-83AC-7D6408B1EC8F}"/>
+    <workbookView xWindow="9210" yWindow="1620" windowWidth="22360" windowHeight="16580" activeTab="3" xr2:uid="{DC9E7F46-E6E4-44BA-83AC-7D6408B1EC8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="VAX-24" sheetId="3" r:id="rId2"/>
-    <sheet name="Model" sheetId="2" r:id="rId3"/>
+    <sheet name="VAX-31" sheetId="4" r:id="rId2"/>
+    <sheet name="VAX-24" sheetId="3" r:id="rId3"/>
+    <sheet name="Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="67">
   <si>
     <t>Price</t>
   </si>
@@ -148,18 +149,12 @@
     <t>aNPV</t>
   </si>
   <si>
-    <t>Q325</t>
-  </si>
-  <si>
     <t>Est. 2013 as SutroVax</t>
   </si>
   <si>
     <t>Phase</t>
   </si>
   <si>
-    <t>III beginning</t>
-  </si>
-  <si>
     <t>MOA</t>
   </si>
   <si>
@@ -167,13 +162,91 @@
   </si>
   <si>
     <t>Economics</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>PPE</t>
+  </si>
+  <si>
+    <t>VAX-A1</t>
+  </si>
+  <si>
+    <t>Indication</t>
+  </si>
+  <si>
+    <t>Group A Strep</t>
+  </si>
+  <si>
+    <t>Pneumococcus</t>
+  </si>
+  <si>
+    <t>Clinical Trials</t>
+  </si>
+  <si>
+    <t>Infant &amp; Adult Pneumococcal</t>
+  </si>
+  <si>
+    <t>enrollment complete</t>
+  </si>
+  <si>
+    <t>Q426 immunogenicity data</t>
+  </si>
+  <si>
+    <t>1H27 immunogenicity data</t>
+  </si>
+  <si>
+    <t>6191 patients across OPUS</t>
+  </si>
+  <si>
+    <t>Phase III "OPUS-1" 4049 adults - non-inferiority vs. Prevnar &amp; Capvaxive</t>
+  </si>
+  <si>
+    <t>Phase III "OPUS-2" 1390 adults with flu vaccine</t>
+  </si>
+  <si>
+    <t>Phase I/II "unprecedented results" - published in Lancet Infectious Disease</t>
+  </si>
+  <si>
+    <t>Phase III "OPUS-3" 752 previously vaccinated adults</t>
+  </si>
+  <si>
+    <t>opsonophagocytic activity (OPA) and immunoglobulin G (IgG) immune responses</t>
+  </si>
+  <si>
+    <t>Phase II dose finding n=900 infants</t>
+  </si>
+  <si>
+    <t>VAX-XL</t>
+  </si>
+  <si>
+    <t>III enrollment complete</t>
+  </si>
+  <si>
+    <t>discontinued?</t>
+  </si>
+  <si>
+    <t>preclinical</t>
+  </si>
+  <si>
+    <t>I/II</t>
+  </si>
+  <si>
+    <t>Gross Margin</t>
+  </si>
+  <si>
+    <t>Competition</t>
+  </si>
+  <si>
+    <t>Prevnar 20, Prevnar 25, Prevnar 35</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -184,6 +257,21 @@
       <u/>
       <sz val="10"/>
       <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -295,7 +383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -315,6 +403,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -655,7 +748,10 @@
   <dimension ref="B2:M58"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
@@ -663,15 +759,17 @@
         <v>8</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="10"/>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
       <c r="I2" s="11"/>
@@ -679,33 +777,42 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>58.63</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
       <c r="I3" s="5"/>
       <c r="K3" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>130.906263</v>
+        <v>144.397682</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="18" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
         <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
       </c>
       <c r="I4" s="5"/>
       <c r="K4" t="s">
@@ -713,25 +820,41 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>7675.0341996899997</v>
+        <v>8282.6510395200003</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
       <c r="I5" s="5"/>
       <c r="K5" t="s">
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <f>281.08+1430.24+959.256</f>
-        <v>2670.576</v>
+        <f>260.843+1476.335+1004.017</f>
+        <v>2741.1950000000002</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="K6" t="s">
         <v>4</v>
@@ -740,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
@@ -751,7 +874,7 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>5004.4581996899997</v>
+        <v>5541.4560395200006</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -765,7 +888,10 @@
         <v>6</v>
       </c>
       <c r="L9" s="2">
-        <v>3132.3180000000002</v>
+        <v>5478.27</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
@@ -781,12 +907,21 @@
         <v>7</v>
       </c>
       <c r="L10" s="2">
-        <v>1148.115</v>
+        <v>2475.569</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K12" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="L12" s="2">
+        <v>260.69499999999999</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
@@ -794,6 +929,9 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="13"/>
+      <c r="K15" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
@@ -925,11 +1063,133 @@
       <c r="B58" s="13"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" location="'VAX-31'!A1" display="VAX-31" xr:uid="{17FA1F4B-E944-406A-B514-D2083D458020}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6211225-6290-4424-AFF5-C82742672405}">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C8" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C12" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="17"/>
+    </row>
+    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C16" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C20" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C23" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{7503C046-0819-4406-B763-104A0D07FBD7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98955C5-2297-46D2-97F5-220A1E65BB8D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -988,9 +1248,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4AEDB0E-BCF2-4DE8-9FB7-6A626C584111}">
-  <dimension ref="A1:DO20"/>
+  <dimension ref="A1:DO21"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1118,84 +1378,84 @@
         <v>0</v>
       </c>
       <c r="F4" s="14">
+        <v>0.01</v>
+      </c>
+      <c r="G4" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="14">
         <v>0.2</v>
       </c>
-      <c r="G4" s="14">
-        <v>0.4</v>
-      </c>
-      <c r="H4" s="14">
-        <v>0.6</v>
-      </c>
       <c r="I4" s="14">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J4" s="14">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="K4" s="14">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="L4" s="14">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="M4" s="14">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="N4" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:119" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:119" s="15" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="19">
         <f>+C3*C4</f>
         <v>0</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="19">
         <f t="shared" ref="D5:N5" si="2">+D3*D4</f>
         <v>0</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="19">
         <f t="shared" si="2"/>
-        <v>1339.3913</v>
-      </c>
-      <c r="G5" s="2">
+        <v>66.969564999999989</v>
+      </c>
+      <c r="G5" s="19">
         <f t="shared" si="2"/>
-        <v>2705.5704260000002</v>
-      </c>
-      <c r="H5" s="2">
+        <v>676.39260650000006</v>
+      </c>
+      <c r="H5" s="19">
         <f t="shared" si="2"/>
-        <v>4098.9391953899994</v>
-      </c>
-      <c r="I5" s="2">
+        <v>1366.31306513</v>
+      </c>
+      <c r="I5" s="19">
         <f t="shared" si="2"/>
-        <v>5519.9047831252001</v>
-      </c>
-      <c r="J5" s="2">
+        <v>2069.9642936719497</v>
+      </c>
+      <c r="J5" s="19">
         <f t="shared" si="2"/>
-        <v>6271.9918098260086</v>
-      </c>
-      <c r="K5" s="2">
+        <v>2090.6639366086697</v>
+      </c>
+      <c r="K5" s="19">
         <f t="shared" si="2"/>
-        <v>7038.5685865825208</v>
-      </c>
-      <c r="L5" s="2">
+        <v>2463.4990053038823</v>
+      </c>
+      <c r="L5" s="19">
         <f t="shared" si="2"/>
-        <v>7108.9542724483463</v>
-      </c>
-      <c r="M5" s="2">
+        <v>2488.1339953569209</v>
+      </c>
+      <c r="M5" s="19">
         <f t="shared" si="2"/>
-        <v>7180.0438151728295</v>
-      </c>
-      <c r="N5" s="2">
+        <v>2513.0153353104902</v>
+      </c>
+      <c r="N5" s="19">
         <f t="shared" si="2"/>
-        <v>7251.8442533245579</v>
+        <v>2538.1454886635952</v>
       </c>
     </row>
     <row r="6" spans="1:119" x14ac:dyDescent="0.25">
@@ -1216,39 +1476,39 @@
       </c>
       <c r="F6" s="2">
         <f t="shared" si="3"/>
-        <v>401.81738999999999</v>
+        <v>20.090869499999997</v>
       </c>
       <c r="G6" s="2">
         <f t="shared" si="3"/>
-        <v>811.67112780000002</v>
+        <v>202.91778195000001</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="3"/>
-        <v>1229.6817586169998</v>
+        <v>409.89391953900002</v>
       </c>
       <c r="I6" s="2">
         <f t="shared" si="3"/>
-        <v>1655.9714349375599</v>
+        <v>620.98928810158486</v>
       </c>
       <c r="J6" s="2">
         <f t="shared" si="3"/>
-        <v>1881.5975429478026</v>
+        <v>627.19918098260086</v>
       </c>
       <c r="K6" s="2">
         <f t="shared" si="3"/>
-        <v>2111.5705759747561</v>
+        <v>739.04970159116465</v>
       </c>
       <c r="L6" s="2">
         <f t="shared" si="3"/>
-        <v>2132.6862817345036</v>
+        <v>746.44019860707624</v>
       </c>
       <c r="M6" s="2">
         <f t="shared" si="3"/>
-        <v>2154.0131445518487</v>
+        <v>753.90460059314705</v>
       </c>
       <c r="N6" s="2">
         <f t="shared" si="3"/>
-        <v>2175.5532759973671</v>
+        <v>761.44364659907853</v>
       </c>
     </row>
     <row r="7" spans="1:119" x14ac:dyDescent="0.25">
@@ -1269,39 +1529,39 @@
       </c>
       <c r="F7" s="2">
         <f t="shared" si="4"/>
-        <v>937.57391000000007</v>
+        <v>46.878695499999992</v>
       </c>
       <c r="G7" s="2">
         <f t="shared" si="4"/>
-        <v>1893.8992982000002</v>
+        <v>473.47482455000005</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="4"/>
-        <v>2869.2574367729994</v>
+        <v>956.41914559099996</v>
       </c>
       <c r="I7" s="2">
         <f t="shared" si="4"/>
-        <v>3863.9333481876401</v>
+        <v>1448.9750055703648</v>
       </c>
       <c r="J7" s="2">
         <f t="shared" si="4"/>
-        <v>4390.3942668782056</v>
+        <v>1463.4647556260688</v>
       </c>
       <c r="K7" s="2">
         <f t="shared" si="4"/>
-        <v>4926.9980106077646</v>
+        <v>1724.4493037127177</v>
       </c>
       <c r="L7" s="2">
         <f t="shared" si="4"/>
-        <v>4976.2679907138427</v>
+        <v>1741.6937967498448</v>
       </c>
       <c r="M7" s="2">
         <f t="shared" si="4"/>
-        <v>5026.0306706209813</v>
+        <v>1759.1107347173431</v>
       </c>
       <c r="N7" s="2">
         <f t="shared" si="4"/>
-        <v>5076.2909773271913</v>
+        <v>1776.7018420645168</v>
       </c>
     </row>
     <row r="8" spans="1:119" x14ac:dyDescent="0.25">
@@ -1363,39 +1623,39 @@
       </c>
       <c r="F9" s="2">
         <f t="shared" si="5"/>
-        <v>437.57391000000007</v>
+        <v>-453.12130450000001</v>
       </c>
       <c r="G9" s="2">
         <f t="shared" si="5"/>
-        <v>1393.8992982000002</v>
+        <v>-26.525175449999949</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="5"/>
-        <v>2569.2574367729994</v>
+        <v>656.41914559099996</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="5"/>
-        <v>3663.9333481876401</v>
+        <v>1248.9750055703648</v>
       </c>
       <c r="J9" s="2">
         <f t="shared" si="5"/>
-        <v>4290.3942668782056</v>
+        <v>1363.4647556260688</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="5"/>
-        <v>4826.9980106077646</v>
+        <v>1624.4493037127177</v>
       </c>
       <c r="L9" s="2">
         <f t="shared" si="5"/>
-        <v>4876.2679907138427</v>
+        <v>1641.6937967498448</v>
       </c>
       <c r="M9" s="2">
         <f t="shared" si="5"/>
-        <v>4926.0306706209813</v>
+        <v>1659.1107347173431</v>
       </c>
       <c r="N9" s="2">
         <f t="shared" si="5"/>
-        <v>4976.2909773271913</v>
+        <v>1676.7018420645168</v>
       </c>
     </row>
     <row r="10" spans="1:119" x14ac:dyDescent="0.25">
@@ -1457,39 +1717,39 @@
       </c>
       <c r="F11" s="2">
         <f t="shared" si="6"/>
-        <v>437.57391000000007</v>
+        <v>-453.12130450000001</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="6"/>
-        <v>1393.8992982000002</v>
+        <v>-26.525175449999949</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="6"/>
-        <v>2569.2574367729994</v>
+        <v>656.41914559099996</v>
       </c>
       <c r="I11" s="2">
         <f t="shared" si="6"/>
-        <v>3663.9333481876401</v>
+        <v>1248.9750055703648</v>
       </c>
       <c r="J11" s="2">
         <f t="shared" si="6"/>
-        <v>4290.3942668782056</v>
+        <v>1363.4647556260688</v>
       </c>
       <c r="K11" s="2">
         <f t="shared" si="6"/>
-        <v>4826.9980106077646</v>
+        <v>1624.4493037127177</v>
       </c>
       <c r="L11" s="2">
         <f t="shared" si="6"/>
-        <v>4876.2679907138427</v>
+        <v>1641.6937967498448</v>
       </c>
       <c r="M11" s="2">
         <f t="shared" si="6"/>
-        <v>4926.0306706209813</v>
+        <v>1659.1107347173431</v>
       </c>
       <c r="N11" s="2">
         <f t="shared" si="6"/>
-        <v>4976.2909773271913</v>
+        <v>1676.7018420645168</v>
       </c>
     </row>
     <row r="12" spans="1:119" x14ac:dyDescent="0.25">
@@ -1510,39 +1770,39 @@
       </c>
       <c r="F12" s="2">
         <f t="shared" si="7"/>
-        <v>87.514782000000025</v>
+        <v>-90.62426090000001</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="7"/>
-        <v>278.77985964000004</v>
+        <v>-5.3050350899999899</v>
       </c>
       <c r="H12" s="2">
         <f t="shared" si="7"/>
-        <v>513.85148735459995</v>
+        <v>131.2838291182</v>
       </c>
       <c r="I12" s="2">
         <f t="shared" si="7"/>
-        <v>732.78666963752812</v>
+        <v>249.79500111407299</v>
       </c>
       <c r="J12" s="2">
         <f t="shared" si="7"/>
-        <v>858.07885337564119</v>
+        <v>272.69295112521377</v>
       </c>
       <c r="K12" s="2">
         <f t="shared" si="7"/>
-        <v>965.39960212155302</v>
+        <v>324.88986074254353</v>
       </c>
       <c r="L12" s="2">
         <f t="shared" si="7"/>
-        <v>975.25359814276862</v>
+        <v>328.338759349969</v>
       </c>
       <c r="M12" s="2">
         <f t="shared" si="7"/>
-        <v>985.2061341241963</v>
+        <v>331.82214694346862</v>
       </c>
       <c r="N12" s="2">
         <f t="shared" si="7"/>
-        <v>995.25819546543835</v>
+        <v>335.34036841290339</v>
       </c>
     </row>
     <row r="13" spans="1:119" x14ac:dyDescent="0.25">
@@ -1563,501 +1823,542 @@
       </c>
       <c r="F13" s="2">
         <f t="shared" si="8"/>
-        <v>350.05912800000004</v>
+        <v>-362.49704359999998</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="8"/>
-        <v>1115.1194385600002</v>
+        <v>-21.220140359999959</v>
       </c>
       <c r="H13" s="2">
         <f t="shared" si="8"/>
-        <v>2055.4059494183994</v>
+        <v>525.13531647280001</v>
       </c>
       <c r="I13" s="2">
         <f t="shared" si="8"/>
-        <v>2931.146678550112</v>
+        <v>999.18000445629184</v>
       </c>
       <c r="J13" s="2">
         <f t="shared" si="8"/>
-        <v>3432.3154135025643</v>
+        <v>1090.7718045008551</v>
       </c>
       <c r="K13" s="2">
         <f t="shared" si="8"/>
-        <v>3861.5984084862116</v>
+        <v>1299.5594429701741</v>
       </c>
       <c r="L13" s="2">
         <f t="shared" si="8"/>
-        <v>3901.014392571074</v>
+        <v>1313.3550373998758</v>
       </c>
       <c r="M13" s="2">
         <f t="shared" si="8"/>
-        <v>3940.8245364967852</v>
+        <v>1327.2885877738745</v>
       </c>
       <c r="N13" s="2">
         <f t="shared" si="8"/>
-        <v>3981.0327818617529</v>
+        <v>1341.3614736516133</v>
       </c>
       <c r="O13" s="2">
-        <f>N13*(1+$P$16)</f>
-        <v>3981.0327818617529</v>
+        <f>N13*(1+$P$17)</f>
+        <v>1274.2933999690326</v>
       </c>
       <c r="P13" s="2">
-        <f t="shared" ref="P13:CA13" si="9">O13*(1+$P$16)</f>
-        <v>3981.0327818617529</v>
+        <f t="shared" ref="P13:CA13" si="9">O13*(1+$P$17)</f>
+        <v>1210.578729970581</v>
       </c>
       <c r="Q13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>1150.049793472052</v>
       </c>
       <c r="R13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>1092.5473037984493</v>
       </c>
       <c r="S13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>1037.9199386085268</v>
       </c>
       <c r="T13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>986.02394167810041</v>
       </c>
       <c r="U13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>936.72274459419532</v>
       </c>
       <c r="V13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>889.88660736448549</v>
       </c>
       <c r="W13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>845.39227699626122</v>
       </c>
       <c r="X13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>803.12266314644808</v>
       </c>
       <c r="Y13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>762.96652998912566</v>
       </c>
       <c r="Z13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>724.81820348966937</v>
       </c>
       <c r="AA13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>688.5772933151859</v>
       </c>
       <c r="AB13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>654.14842864942659</v>
       </c>
       <c r="AC13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>621.4410072169552</v>
       </c>
       <c r="AD13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>590.36895685610739</v>
       </c>
       <c r="AE13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>560.85050901330203</v>
       </c>
       <c r="AF13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>532.80798356263688</v>
       </c>
       <c r="AG13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>506.16758438450501</v>
       </c>
       <c r="AH13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>480.85920516527972</v>
       </c>
       <c r="AI13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>456.81624490701569</v>
       </c>
       <c r="AJ13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>433.97543266166485</v>
       </c>
       <c r="AK13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>412.2766610285816</v>
       </c>
       <c r="AL13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>391.66282797715252</v>
       </c>
       <c r="AM13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>372.07968657829485</v>
       </c>
       <c r="AN13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>353.47570224938011</v>
       </c>
       <c r="AO13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>335.80191713691107</v>
       </c>
       <c r="AP13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>319.01182128006548</v>
       </c>
       <c r="AQ13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>303.0612302160622</v>
       </c>
       <c r="AR13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>287.90816870525907</v>
       </c>
       <c r="AS13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>273.51276026999608</v>
       </c>
       <c r="AT13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>259.83712225649629</v>
       </c>
       <c r="AU13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>246.84526614367147</v>
       </c>
       <c r="AV13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>234.50300283648789</v>
       </c>
       <c r="AW13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>222.77785269466349</v>
       </c>
       <c r="AX13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>211.6389600599303</v>
       </c>
       <c r="AY13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>201.05701205693379</v>
       </c>
       <c r="AZ13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>191.0041614540871</v>
       </c>
       <c r="BA13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>181.45395338138275</v>
       </c>
       <c r="BB13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>172.38125571231359</v>
       </c>
       <c r="BC13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>163.76219292669791</v>
       </c>
       <c r="BD13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>155.574083280363</v>
       </c>
       <c r="BE13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>147.79537911634483</v>
       </c>
       <c r="BF13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>140.40561016052757</v>
       </c>
       <c r="BG13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>133.38532965250118</v>
       </c>
       <c r="BH13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>126.71606316987612</v>
       </c>
       <c r="BI13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>120.3802600113823</v>
       </c>
       <c r="BJ13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>114.36124701081319</v>
       </c>
       <c r="BK13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>108.64318466027252</v>
       </c>
       <c r="BL13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>103.21102542725889</v>
       </c>
       <c r="BM13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>98.050474155895941</v>
       </c>
       <c r="BN13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>93.147950448101142</v>
       </c>
       <c r="BO13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>88.490552925696079</v>
       </c>
       <c r="BP13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>84.066025279411278</v>
       </c>
       <c r="BQ13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>79.862724015440705</v>
       </c>
       <c r="BR13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>75.869587814668662</v>
       </c>
       <c r="BS13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>72.076108423935224</v>
       </c>
       <c r="BT13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>68.472303002738457</v>
       </c>
       <c r="BU13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>65.048687852601532</v>
       </c>
       <c r="BV13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>61.796253459971453</v>
       </c>
       <c r="BW13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>58.706440786972877</v>
       </c>
       <c r="BX13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>55.771118747624229</v>
       </c>
       <c r="BY13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>52.982562810243017</v>
       </c>
       <c r="BZ13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>50.333434669730863</v>
       </c>
       <c r="CA13" s="2">
         <f t="shared" si="9"/>
-        <v>3981.0327818617529</v>
+        <v>47.816762936244317</v>
       </c>
       <c r="CB13" s="2">
-        <f t="shared" ref="CB13:DO13" si="10">CA13*(1+$P$16)</f>
-        <v>3981.0327818617529</v>
+        <f t="shared" ref="CB13:DO13" si="10">CA13*(1+$P$17)</f>
+        <v>45.425924789432102</v>
       </c>
       <c r="CC13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>43.154628549960492</v>
       </c>
       <c r="CD13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>40.996897122462464</v>
       </c>
       <c r="CE13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>38.947052266339341</v>
       </c>
       <c r="CF13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>36.999699653022375</v>
       </c>
       <c r="CG13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>35.149714670371253</v>
       </c>
       <c r="CH13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>33.392228936852689</v>
       </c>
       <c r="CI13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>31.722617490010052</v>
       </c>
       <c r="CJ13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>30.136486615509547</v>
       </c>
       <c r="CK13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>28.629662284734067</v>
       </c>
       <c r="CL13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>27.198179170497362</v>
       </c>
       <c r="CM13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>25.838270211972493</v>
       </c>
       <c r="CN13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>24.546356701373867</v>
       </c>
       <c r="CO13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>23.319038866305171</v>
       </c>
       <c r="CP13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>22.15308692298991</v>
       </c>
       <c r="CQ13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>21.045432576840415</v>
       </c>
       <c r="CR13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>19.993160947998394</v>
       </c>
       <c r="CS13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>18.993502900598472</v>
       </c>
       <c r="CT13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>18.043827755568547</v>
       </c>
       <c r="CU13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>17.14163636779012</v>
       </c>
       <c r="CV13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>16.284554549400614</v>
       </c>
       <c r="CW13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>15.470326821930582</v>
       </c>
       <c r="CX13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>14.696810480834053</v>
       </c>
       <c r="CY13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>13.96196995679235</v>
       </c>
       <c r="CZ13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>13.263871458952732</v>
       </c>
       <c r="DA13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>12.600677886005094</v>
       </c>
       <c r="DB13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>11.970643991704838</v>
       </c>
       <c r="DC13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>11.372111792119595</v>
       </c>
       <c r="DD13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>10.803506202513615</v>
       </c>
       <c r="DE13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>10.263330892387934</v>
       </c>
       <c r="DF13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>9.7501643477685374</v>
       </c>
       <c r="DG13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>9.26265613038011</v>
       </c>
       <c r="DH13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>8.7995233238611039</v>
       </c>
       <c r="DI13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>8.3595471576680485</v>
       </c>
       <c r="DJ13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>7.9415697997846459</v>
       </c>
       <c r="DK13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>7.5444913097954132</v>
       </c>
       <c r="DL13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>7.1672667443056426</v>
       </c>
       <c r="DM13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>6.8089034070903605</v>
       </c>
       <c r="DN13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
+        <v>6.4684582367358425</v>
       </c>
       <c r="DO13" s="2">
         <f t="shared" si="10"/>
-        <v>3981.0327818617529</v>
-      </c>
-    </row>
-    <row r="16" spans="1:119" x14ac:dyDescent="0.25">
-      <c r="O16" t="s">
-        <v>31</v>
-      </c>
-      <c r="P16" s="14">
-        <v>0</v>
+        <v>6.1450353248990499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:119" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="14">
+        <f>F7/F5</f>
+        <v>0.7</v>
+      </c>
+      <c r="G15" s="14">
+        <f t="shared" ref="G15:N15" si="11">G7/G5</f>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="H15" s="14">
+        <f t="shared" si="11"/>
+        <v>0.7</v>
+      </c>
+      <c r="I15" s="14">
+        <f t="shared" si="11"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="J15" s="14">
+        <f t="shared" si="11"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="K15" s="14">
+        <f t="shared" si="11"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="L15" s="14">
+        <f t="shared" si="11"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="M15" s="14">
+        <f t="shared" si="11"/>
+        <v>0.7</v>
+      </c>
+      <c r="N15" s="14">
+        <f t="shared" si="11"/>
+        <v>0.70000000000000007</v>
       </c>
     </row>
     <row r="17" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P17" s="14">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="18" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P18" s="2">
-        <f>NPV(P17,D13:DO13)</f>
-        <v>30103.067660800829</v>
+        <v>32</v>
+      </c>
+      <c r="P18" s="14">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O19" t="s">
-        <v>34</v>
-      </c>
-      <c r="P19" s="14">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="P19" s="2">
+        <f>NPV(P18,G13:DR13)+F13</f>
+        <v>8366.1757364881905</v>
       </c>
     </row>
     <row r="20" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O20" t="s">
+        <v>34</v>
+      </c>
+      <c r="P20" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="15:16" x14ac:dyDescent="0.25">
+      <c r="O21" t="s">
         <v>35</v>
       </c>
-      <c r="P20" s="2">
-        <f>+P18*P19</f>
-        <v>30103.067660800829</v>
+      <c r="P21" s="2">
+        <f>+P19*P20</f>
+        <v>8366.1757364881905</v>
       </c>
     </row>
   </sheetData>
